--- a/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>BIP</t>
   </si>
@@ -656,197 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>17931000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14427000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11537000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8885000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6597000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4652000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3535000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2115000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1855000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1924000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1826000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1524000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1115000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13470000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8352000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8247000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4843000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3395000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2208000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1509000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1063000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>798000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>846000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>823000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>766000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>561000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4461000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6075000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3290000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4042000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3202000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2444000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2026000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1052000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1057000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1078000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1003000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>758000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>554000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +876,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +918,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,9 +963,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -961,78 +981,84 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>3000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-338000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-53000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3">
         <v>2158000</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1705000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1214000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>801000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>671000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>447000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>375000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>380000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>329000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>230000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>126000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1072,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <v>10943000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8653000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6860000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4891000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2894000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2419000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1676000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1307000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1341000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1209000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1091000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>748000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>3484000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2884000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2025000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1706000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1758000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1116000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>439000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>548000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>583000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>617000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>433000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>367000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1181,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>306000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1917000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>349000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>126000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-33000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>59000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>496000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>206000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>95000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>40000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-40000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>51000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3">
         <v>5948000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6837000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4079000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3046000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2526000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1846000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1382000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1129000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1058000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>986000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>625000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>545000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2501000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1855000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1468000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1179000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>904000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>555000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>428000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>392000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>367000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>362000</v>
       </c>
       <c r="M22" s="3">
         <v>362000</v>
       </c>
       <c r="N22" s="3">
+        <v>362000</v>
+      </c>
+      <c r="O22" s="3">
         <v>322000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>253000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2029000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1935000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3333000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1195000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>928000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1170000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>747000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>543000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>387000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>316000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>295000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>71000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>165000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>581000</v>
+      </c>
+      <c r="E24" s="3">
         <v>560000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>614000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>291000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>278000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>364000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>173000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>79000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-30000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1448,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>1375000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2719000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>904000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>650000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>806000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>574000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>528000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>391000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>237000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>293000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>101000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>151000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>87000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>613000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>121000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>30000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>163000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>276000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>166000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>109000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>165000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-126000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-158000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1583,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1556,20 +1617,23 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-8000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-228000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>190000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>289000</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1673,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1718,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>-306000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1917000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-349000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-126000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>33000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-59000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-496000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-206000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-95000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-40000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>40000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-51000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>87000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>613000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>121000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>163000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>276000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>166000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>101000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-63000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>64000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>131000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1853,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>87000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>613000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>121000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>163000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>276000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>166000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>101000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-63000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>64000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>131000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1970,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,386 +1989,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1857000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1138000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1250000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>742000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>595000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>390000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>341000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>702000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>199000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>189000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>538000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>526000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>306000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>787000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1073000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>655000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>619000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>346000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>296000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>95000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>135000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>432000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>478000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>260000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>23000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>2342000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1923000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1531000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1802000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1105000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>781000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>468000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>300000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>268000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>313000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>372000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>179000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>531000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>400000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>221000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>242000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>141000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>108000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>101000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>21000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>22000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>108000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>87000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>1602000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>668000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>598000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2856000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>344000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>187000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>226000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>609000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>604000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>135000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>140000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>72000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2644000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6686000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4896000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3711000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5841000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2276000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1512000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1632000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1553000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1560000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1268000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>746000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>478000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5402000</v>
+      </c>
+      <c r="E47" s="3">
         <v>6583000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5658000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6371000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5079000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4775000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5834000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4954000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4234000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2412000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2039000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2179000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1400000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52879000</v>
+      </c>
+      <c r="E48" s="3">
         <v>37991000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39310000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32102000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23429000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13004000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10129000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8810000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7785000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8246000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7927000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19150000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7107000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>30333000</v>
+      </c>
+      <c r="E49" s="3">
         <v>20611000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23193000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18401000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>20939000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15494000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11195000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4967000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3375000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3659000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4054000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9630000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3515000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2436,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2481,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9526000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1098000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>904000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>746000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1020000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1031000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>807000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>912000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>788000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>618000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>394000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1454000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>719000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2571,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>100784000</v>
+      </c>
+      <c r="E54" s="3">
         <v>72969000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73961000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>61331000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>56308000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36580000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29477000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21275000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17735000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16495000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15682000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19718000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13269000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2638,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,260 +2657,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>1872000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1877000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1461000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>854000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>463000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>246000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>266000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>196000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>264000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>222000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>842000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>166000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
         <v>3415000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3548000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1757000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1578000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>985000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>463000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>574000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>302000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>41000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>71000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>663000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>145000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>3090000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3236000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2306000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3007000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>969000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>855000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>675000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>712000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>516000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>305000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>414000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>226000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>8377000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8661000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5524000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5439000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2417000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1564000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1515000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1210000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>821000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>598000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1291000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>526000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45815000</v>
+      </c>
+      <c r="E61" s="3">
         <v>30259000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29564000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25244000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21264000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14141000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9721000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7772000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6950000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6788000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6116000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8115000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4760000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20953000</v>
+      </c>
+      <c r="E62" s="3">
         <v>8779000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9345000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8890000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7428000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5354000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4718000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2344000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2399000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2564000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2363000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3863000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2328000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2969,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3014,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3059,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>94224000</v>
+      </c>
+      <c r="E66" s="3">
         <v>65070000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>65721000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55311000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>50301000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31109000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23890000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16262000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13685000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12938000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11904000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16059000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10196000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3126,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3168,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,51 +3213,57 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E70" s="3">
         <v>27000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>31000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>19000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>24000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>22000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>25000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>27000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>23000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>24000</v>
-      </c>
-      <c r="M70" s="3">
-        <v>27000</v>
       </c>
       <c r="N70" s="3">
         <v>27000</v>
       </c>
       <c r="O70" s="3">
+        <v>27000</v>
+      </c>
+      <c r="P70" s="3">
         <v>26000</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3303,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2657000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2125000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2285000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1430000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-856000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-953000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-483000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-559000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-400000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-213000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>189000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3393,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3438,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3483,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6532000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7872000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8209000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6001000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5983000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5449000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5562000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4986000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4027000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3533000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3751000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3632000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3047000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3573,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>87000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>613000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>121000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>163000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>276000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>166000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>101000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-63000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>64000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>131000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3690,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2739000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2158000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2036000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1705000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1214000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>801000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>671000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>447000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>375000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>380000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>329000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>232000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>127000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3777,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3822,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3867,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3912,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3957,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4078000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3094000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2772000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2530000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2130000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1362000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1481000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>753000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>632000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>691000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>694000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>635000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>340000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4024,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12470000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2775000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2067000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1472000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1182000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-839000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-714000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-690000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-520000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-454000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-425000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-654000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-508000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4111,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4156,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12990000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3365000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1173000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4609000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11372000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5564000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5721000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1058000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2346000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1073000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-162000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1764000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-763000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,50 +4223,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1516000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1174000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-1048000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-949000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-869000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-779000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-680000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-544000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-480000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-402000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-356000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-288000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-218000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4310,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4355,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4400,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9419000</v>
+      </c>
+      <c r="E100" s="3">
         <v>56000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-995000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2126000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9542000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4418000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3814000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>899000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1764000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>42000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-232000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1238000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>411000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E101" s="3">
         <v>88000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-65000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-50000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-32000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-25000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>11000</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>578000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-127000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>539000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>40000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>287000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>166000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-412000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>587000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-349000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>275000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>110000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>BIP</t>
   </si>
@@ -774,7 +774,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>13470000</v>
+        <v>10731000</v>
       </c>
       <c r="E9" s="3">
         <v>8352000</v>
@@ -819,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4461000</v>
+        <v>7200000</v>
       </c>
       <c r="E10" s="3">
         <v>6075000</v>
@@ -1017,8 +1017,8 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>2739000</v>
       </c>
       <c r="E15" s="3">
         <v>2158000</v>
@@ -1078,8 +1078,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>13883000</v>
       </c>
       <c r="E17" s="3">
         <v>10943000</v>
@@ -1123,8 +1123,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>4048000</v>
       </c>
       <c r="E18" s="3">
         <v>3484000</v>
@@ -1187,8 +1187,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>482000</v>
       </c>
       <c r="E20" s="3">
         <v>306000</v>
@@ -1232,8 +1232,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>7269000</v>
       </c>
       <c r="E21" s="3">
         <v>5948000</v>
@@ -1457,8 +1457,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>1448000</v>
       </c>
       <c r="E26" s="3">
         <v>1375000</v>
@@ -1502,8 +1502,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>87000</v>
       </c>
       <c r="E27" s="3">
         <v>87000</v>
@@ -1727,8 +1727,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-482000</v>
       </c>
       <c r="E32" s="3">
         <v>-306000</v>
@@ -1772,8 +1772,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>87000</v>
       </c>
       <c r="E33" s="3">
         <v>87000</v>
@@ -1862,8 +1862,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>87000</v>
       </c>
       <c r="E35" s="3">
         <v>87000</v>
@@ -1996,7 +1996,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1857000</v>
+        <v>1641000</v>
       </c>
       <c r="E41" s="3">
         <v>1138000</v>
@@ -2041,7 +2041,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>787000</v>
+        <v>696000</v>
       </c>
       <c r="E42" s="3">
         <v>1073000</v>
@@ -2085,8 +2085,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3">
+        <v>3734000</v>
       </c>
       <c r="E43" s="3">
         <v>2342000</v>
@@ -2130,8 +2130,8 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>512000</v>
       </c>
       <c r="E44" s="3">
         <v>531000</v>
@@ -2175,8 +2175,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>1396000</v>
       </c>
       <c r="E45" s="3">
         <v>1602000</v>
@@ -2221,7 +2221,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2644000</v>
+        <v>7979000</v>
       </c>
       <c r="E46" s="3">
         <v>6686000</v>
@@ -2266,7 +2266,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5402000</v>
+        <v>8491000</v>
       </c>
       <c r="E47" s="3">
         <v>6583000</v>
@@ -2491,7 +2491,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9526000</v>
+        <v>1102000</v>
       </c>
       <c r="E52" s="3">
         <v>1098000</v>
@@ -2663,8 +2663,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>2253000</v>
       </c>
       <c r="E57" s="3">
         <v>1872000</v>
@@ -2708,17 +2708,17 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>6484000</v>
       </c>
       <c r="E58" s="3">
-        <v>3415000</v>
+        <v>3562000</v>
       </c>
       <c r="F58" s="3">
         <v>3548000</v>
       </c>
       <c r="G58" s="3">
-        <v>1757000</v>
+        <v>1891000</v>
       </c>
       <c r="H58" s="3">
         <v>1578000</v>
@@ -2753,17 +2753,17 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>2968000</v>
       </c>
       <c r="E59" s="3">
-        <v>3090000</v>
+        <v>2943000</v>
       </c>
       <c r="F59" s="3">
         <v>3236000</v>
       </c>
       <c r="G59" s="3">
-        <v>2306000</v>
+        <v>2172000</v>
       </c>
       <c r="H59" s="3">
         <v>3007000</v>
@@ -2798,8 +2798,8 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>8</v>
+      <c r="D60" s="3">
+        <v>11705000</v>
       </c>
       <c r="E60" s="3">
         <v>8377000</v>
@@ -2844,16 +2844,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>45815000</v>
+        <v>43110000</v>
       </c>
       <c r="E61" s="3">
-        <v>30259000</v>
+        <v>30286000</v>
       </c>
       <c r="F61" s="3">
-        <v>29564000</v>
+        <v>29592000</v>
       </c>
       <c r="G61" s="3">
-        <v>25244000</v>
+        <v>25328000</v>
       </c>
       <c r="H61" s="3">
         <v>21264000</v>
@@ -2889,16 +2889,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20953000</v>
+        <v>11953000</v>
       </c>
       <c r="E62" s="3">
-        <v>8779000</v>
+        <v>8752000</v>
       </c>
       <c r="F62" s="3">
-        <v>9345000</v>
+        <v>9317000</v>
       </c>
       <c r="G62" s="3">
-        <v>8890000</v>
+        <v>8806000</v>
       </c>
       <c r="H62" s="3">
         <v>7428000</v>
@@ -3069,7 +3069,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>94224000</v>
+        <v>92691000</v>
       </c>
       <c r="E66" s="3">
         <v>65070000</v>
@@ -3312,8 +3312,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>-3246000</v>
       </c>
       <c r="E72" s="3">
         <v>-2657000</v>
@@ -3493,7 +3493,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6532000</v>
+        <v>8065000</v>
       </c>
       <c r="E76" s="3">
         <v>7872000</v>
@@ -3632,8 +3632,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>87000</v>
       </c>
       <c r="E81" s="3">
         <v>87000</v>
@@ -4031,7 +4031,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-12470000</v>
+        <v>-2487000</v>
       </c>
       <c r="E91" s="3">
         <v>-2775000</v>
@@ -4230,7 +4230,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1516000</v>
+        <v>-1247000</v>
       </c>
       <c r="E96" s="3">
         <v>-1174000</v>

--- a/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>BIP</t>
   </si>
@@ -774,19 +774,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>10731000</v>
+        <v>13470000</v>
       </c>
       <c r="E9" s="3">
-        <v>8352000</v>
+        <v>10510000</v>
       </c>
       <c r="F9" s="3">
         <v>8247000</v>
       </c>
       <c r="G9" s="3">
-        <v>4843000</v>
+        <v>6548000</v>
       </c>
       <c r="H9" s="3">
-        <v>3395000</v>
+        <v>4609000</v>
       </c>
       <c r="I9" s="3">
         <v>2208000</v>
@@ -819,19 +819,19 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7200000</v>
+        <v>4461000</v>
       </c>
       <c r="E10" s="3">
-        <v>6075000</v>
+        <v>3917000</v>
       </c>
       <c r="F10" s="3">
         <v>3290000</v>
       </c>
       <c r="G10" s="3">
-        <v>4042000</v>
+        <v>2337000</v>
       </c>
       <c r="H10" s="3">
-        <v>3202000</v>
+        <v>1988000</v>
       </c>
       <c r="I10" s="3">
         <v>2444000</v>
@@ -972,20 +972,20 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-2100000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>3000</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>-338000</v>
@@ -1023,8 +1023,8 @@
       <c r="E15" s="3">
         <v>2158000</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
+      <c r="F15" s="3">
+        <v>2036000</v>
       </c>
       <c r="G15" s="3">
         <v>1705000</v>
@@ -1091,10 +1091,10 @@
         <v>6860000</v>
       </c>
       <c r="H17" s="3">
-        <v>4891000</v>
+        <v>4888000</v>
       </c>
       <c r="I17" s="3">
-        <v>2894000</v>
+        <v>3232000</v>
       </c>
       <c r="J17" s="3">
         <v>2419000</v>
@@ -1136,10 +1136,10 @@
         <v>2025000</v>
       </c>
       <c r="H18" s="3">
-        <v>1706000</v>
+        <v>1709000</v>
       </c>
       <c r="I18" s="3">
-        <v>1758000</v>
+        <v>1420000</v>
       </c>
       <c r="J18" s="3">
         <v>1116000</v>
@@ -1188,25 +1188,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>482000</v>
+        <v>-480000</v>
       </c>
       <c r="E20" s="3">
-        <v>306000</v>
+        <v>-266000</v>
       </c>
       <c r="F20" s="3">
-        <v>1917000</v>
+        <v>183000</v>
       </c>
       <c r="G20" s="3">
-        <v>349000</v>
+        <v>-349000</v>
       </c>
       <c r="H20" s="3">
-        <v>126000</v>
+        <v>-123000</v>
       </c>
       <c r="I20" s="3">
-        <v>-33000</v>
+        <v>33000</v>
       </c>
       <c r="J20" s="3">
-        <v>59000</v>
+        <v>-59000</v>
       </c>
       <c r="K20" s="3">
         <v>496000</v>
@@ -1233,13 +1233,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7269000</v>
+        <v>7267000</v>
       </c>
       <c r="E21" s="3">
-        <v>5948000</v>
+        <v>5908000</v>
       </c>
       <c r="F21" s="3">
-        <v>6837000</v>
+        <v>4737000</v>
       </c>
       <c r="G21" s="3">
         <v>4079000</v>
@@ -1248,7 +1248,7 @@
         <v>3046000</v>
       </c>
       <c r="I21" s="3">
-        <v>2526000</v>
+        <v>2188000</v>
       </c>
       <c r="J21" s="3">
         <v>1846000</v>
@@ -1515,7 +1515,7 @@
         <v>121000</v>
       </c>
       <c r="H27" s="3">
-        <v>30000</v>
+        <v>19000</v>
       </c>
       <c r="I27" s="3">
         <v>163000</v>
@@ -1728,25 +1728,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-482000</v>
+        <v>480000</v>
       </c>
       <c r="E32" s="3">
-        <v>-306000</v>
+        <v>266000</v>
       </c>
       <c r="F32" s="3">
-        <v>-1917000</v>
+        <v>-183000</v>
       </c>
       <c r="G32" s="3">
-        <v>-349000</v>
+        <v>349000</v>
       </c>
       <c r="H32" s="3">
-        <v>-126000</v>
+        <v>123000</v>
       </c>
       <c r="I32" s="3">
-        <v>33000</v>
+        <v>-33000</v>
       </c>
       <c r="J32" s="3">
-        <v>-59000</v>
+        <v>59000</v>
       </c>
       <c r="K32" s="3">
         <v>-496000</v>
@@ -1773,25 +1773,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>87000</v>
+        <v>125000</v>
       </c>
       <c r="E33" s="3">
-        <v>87000</v>
+        <v>125000</v>
       </c>
       <c r="F33" s="3">
-        <v>613000</v>
+        <v>654000</v>
       </c>
       <c r="G33" s="3">
-        <v>121000</v>
+        <v>156000</v>
       </c>
       <c r="H33" s="3">
-        <v>30000</v>
+        <v>52000</v>
       </c>
       <c r="I33" s="3">
-        <v>163000</v>
+        <v>192000</v>
       </c>
       <c r="J33" s="3">
-        <v>-11000</v>
+        <v>11000</v>
       </c>
       <c r="K33" s="3">
         <v>276000</v>
@@ -1863,25 +1863,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>87000</v>
+        <v>125000</v>
       </c>
       <c r="E35" s="3">
-        <v>87000</v>
+        <v>125000</v>
       </c>
       <c r="F35" s="3">
-        <v>613000</v>
+        <v>654000</v>
       </c>
       <c r="G35" s="3">
-        <v>121000</v>
+        <v>156000</v>
       </c>
       <c r="H35" s="3">
-        <v>30000</v>
+        <v>52000</v>
       </c>
       <c r="I35" s="3">
-        <v>163000</v>
+        <v>192000</v>
       </c>
       <c r="J35" s="3">
-        <v>-11000</v>
+        <v>11000</v>
       </c>
       <c r="K35" s="3">
         <v>276000</v>
@@ -1996,25 +1996,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1641000</v>
+        <v>1857000</v>
       </c>
       <c r="E41" s="3">
-        <v>1138000</v>
+        <v>1279000</v>
       </c>
       <c r="F41" s="3">
-        <v>1250000</v>
+        <v>1406000</v>
       </c>
       <c r="G41" s="3">
-        <v>742000</v>
+        <v>867000</v>
       </c>
       <c r="H41" s="3">
-        <v>595000</v>
+        <v>827000</v>
       </c>
       <c r="I41" s="3">
-        <v>390000</v>
+        <v>540000</v>
       </c>
       <c r="J41" s="3">
-        <v>341000</v>
+        <v>374000</v>
       </c>
       <c r="K41" s="3">
         <v>702000</v>
@@ -2041,25 +2041,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>696000</v>
+        <v>843000</v>
       </c>
       <c r="E42" s="3">
-        <v>1073000</v>
+        <v>1239000</v>
       </c>
       <c r="F42" s="3">
-        <v>655000</v>
+        <v>614000</v>
       </c>
       <c r="G42" s="3">
-        <v>619000</v>
+        <v>596000</v>
       </c>
       <c r="H42" s="3">
-        <v>346000</v>
+        <v>259000</v>
       </c>
       <c r="I42" s="3">
-        <v>296000</v>
+        <v>240000</v>
       </c>
       <c r="J42" s="3">
-        <v>95000</v>
+        <v>139000</v>
       </c>
       <c r="K42" s="3">
         <v>135000</v>
@@ -2095,7 +2095,7 @@
         <v>1923000</v>
       </c>
       <c r="G43" s="3">
-        <v>1531000</v>
+        <v>1543000</v>
       </c>
       <c r="H43" s="3">
         <v>1802000</v>
@@ -2176,25 +2176,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1396000</v>
+        <v>23000</v>
       </c>
       <c r="E45" s="3">
-        <v>1602000</v>
+        <v>980000</v>
       </c>
       <c r="F45" s="3">
-        <v>668000</v>
+        <v>225000</v>
       </c>
       <c r="G45" s="3">
-        <v>598000</v>
+        <v>34000</v>
       </c>
       <c r="H45" s="3">
-        <v>2856000</v>
+        <v>2492000</v>
       </c>
       <c r="I45" s="3">
-        <v>344000</v>
+        <v>123000</v>
       </c>
       <c r="J45" s="3">
-        <v>187000</v>
+        <v>10000</v>
       </c>
       <c r="K45" s="3">
         <v>226000</v>
@@ -2266,25 +2266,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8491000</v>
+        <v>5934000</v>
       </c>
       <c r="E47" s="3">
-        <v>6583000</v>
+        <v>5981000</v>
       </c>
       <c r="F47" s="3">
-        <v>5658000</v>
+        <v>5174000</v>
       </c>
       <c r="G47" s="3">
-        <v>6371000</v>
+        <v>5897000</v>
       </c>
       <c r="H47" s="3">
-        <v>5079000</v>
+        <v>5616000</v>
       </c>
       <c r="I47" s="3">
-        <v>4775000</v>
+        <v>5297000</v>
       </c>
       <c r="J47" s="3">
-        <v>5834000</v>
+        <v>5866000</v>
       </c>
       <c r="K47" s="3">
         <v>4954000</v>
@@ -2311,25 +2311,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>52879000</v>
+        <v>48546000</v>
       </c>
       <c r="E48" s="3">
-        <v>37991000</v>
+        <v>37291000</v>
       </c>
       <c r="F48" s="3">
-        <v>39310000</v>
+        <v>38655000</v>
       </c>
       <c r="G48" s="3">
-        <v>32102000</v>
+        <v>31584000</v>
       </c>
       <c r="H48" s="3">
-        <v>23429000</v>
+        <v>23013000</v>
       </c>
       <c r="I48" s="3">
-        <v>13004000</v>
+        <v>12814000</v>
       </c>
       <c r="J48" s="3">
-        <v>10129000</v>
+        <v>9937000</v>
       </c>
       <c r="K48" s="3">
         <v>8810000</v>
@@ -2491,25 +2491,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1102000</v>
+        <v>5090000</v>
       </c>
       <c r="E52" s="3">
-        <v>1098000</v>
+        <v>1259000</v>
       </c>
       <c r="F52" s="3">
-        <v>904000</v>
+        <v>1153000</v>
       </c>
       <c r="G52" s="3">
-        <v>746000</v>
+        <v>1012000</v>
       </c>
       <c r="H52" s="3">
-        <v>1020000</v>
+        <v>702000</v>
       </c>
       <c r="I52" s="3">
-        <v>1031000</v>
+        <v>527000</v>
       </c>
       <c r="J52" s="3">
-        <v>807000</v>
+        <v>691000</v>
       </c>
       <c r="K52" s="3">
         <v>912000</v>
@@ -2676,7 +2676,7 @@
         <v>1461000</v>
       </c>
       <c r="H57" s="3">
-        <v>854000</v>
+        <v>973000</v>
       </c>
       <c r="I57" s="3">
         <v>463000</v>
@@ -2709,16 +2709,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6484000</v>
+        <v>6571000</v>
       </c>
       <c r="E58" s="3">
-        <v>3562000</v>
+        <v>3634000</v>
       </c>
       <c r="F58" s="3">
-        <v>3548000</v>
+        <v>3602000</v>
       </c>
       <c r="G58" s="3">
-        <v>1891000</v>
+        <v>2007000</v>
       </c>
       <c r="H58" s="3">
         <v>1578000</v>
@@ -2754,25 +2754,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2968000</v>
+        <v>1155000</v>
       </c>
       <c r="E59" s="3">
-        <v>2943000</v>
+        <v>1476000</v>
       </c>
       <c r="F59" s="3">
-        <v>3236000</v>
+        <v>2079000</v>
       </c>
       <c r="G59" s="3">
-        <v>2172000</v>
+        <v>1305000</v>
       </c>
       <c r="H59" s="3">
-        <v>3007000</v>
+        <v>2235000</v>
       </c>
       <c r="I59" s="3">
-        <v>969000</v>
+        <v>384000</v>
       </c>
       <c r="J59" s="3">
-        <v>855000</v>
+        <v>455000</v>
       </c>
       <c r="K59" s="3">
         <v>675000</v>
@@ -2844,25 +2844,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>43110000</v>
+        <v>43377000</v>
       </c>
       <c r="E61" s="3">
-        <v>30286000</v>
+        <v>30306000</v>
       </c>
       <c r="F61" s="3">
-        <v>29592000</v>
+        <v>29752000</v>
       </c>
       <c r="G61" s="3">
-        <v>25328000</v>
+        <v>25669000</v>
       </c>
       <c r="H61" s="3">
-        <v>21264000</v>
+        <v>21476000</v>
       </c>
       <c r="I61" s="3">
-        <v>14141000</v>
+        <v>14241000</v>
       </c>
       <c r="J61" s="3">
-        <v>9721000</v>
+        <v>9730000</v>
       </c>
       <c r="K61" s="3">
         <v>7772000</v>
@@ -2889,25 +2889,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11953000</v>
+        <v>3285000</v>
       </c>
       <c r="E62" s="3">
-        <v>8752000</v>
+        <v>2495000</v>
       </c>
       <c r="F62" s="3">
-        <v>9317000</v>
+        <v>2608000</v>
       </c>
       <c r="G62" s="3">
-        <v>8806000</v>
+        <v>3071000</v>
       </c>
       <c r="H62" s="3">
-        <v>7428000</v>
+        <v>2202000</v>
       </c>
       <c r="I62" s="3">
-        <v>5354000</v>
+        <v>1429000</v>
       </c>
       <c r="J62" s="3">
-        <v>4718000</v>
+        <v>1460000</v>
       </c>
       <c r="K62" s="3">
         <v>2344000</v>
@@ -3069,25 +3069,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>92691000</v>
+        <v>66768000</v>
       </c>
       <c r="E66" s="3">
-        <v>65070000</v>
+        <v>47415000</v>
       </c>
       <c r="F66" s="3">
-        <v>65721000</v>
+        <v>47570000</v>
       </c>
       <c r="G66" s="3">
-        <v>55311000</v>
+        <v>39658000</v>
       </c>
       <c r="H66" s="3">
-        <v>50301000</v>
+        <v>34131000</v>
       </c>
       <c r="I66" s="3">
-        <v>31109000</v>
+        <v>21912000</v>
       </c>
       <c r="J66" s="3">
-        <v>23890000</v>
+        <v>16003000</v>
       </c>
       <c r="K66" s="3">
         <v>16262000</v>
@@ -3223,25 +3223,25 @@
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>28000</v>
+        <v>918000</v>
       </c>
       <c r="E70" s="3">
-        <v>27000</v>
+        <v>918000</v>
       </c>
       <c r="F70" s="3">
-        <v>31000</v>
+        <v>1138000</v>
       </c>
       <c r="G70" s="3">
-        <v>19000</v>
+        <v>1130000</v>
       </c>
       <c r="H70" s="3">
-        <v>24000</v>
+        <v>935000</v>
       </c>
       <c r="I70" s="3">
-        <v>22000</v>
+        <v>936000</v>
       </c>
       <c r="J70" s="3">
-        <v>25000</v>
+        <v>595000</v>
       </c>
       <c r="K70" s="3">
         <v>27000</v>
@@ -3493,25 +3493,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8065000</v>
+        <v>5321000</v>
       </c>
       <c r="E76" s="3">
-        <v>7872000</v>
+        <v>5372000</v>
       </c>
       <c r="F76" s="3">
-        <v>8209000</v>
+        <v>5702000</v>
       </c>
       <c r="G76" s="3">
-        <v>6001000</v>
+        <v>4233000</v>
       </c>
       <c r="H76" s="3">
-        <v>5983000</v>
+        <v>5048000</v>
       </c>
       <c r="I76" s="3">
-        <v>5449000</v>
+        <v>4513000</v>
       </c>
       <c r="J76" s="3">
-        <v>5562000</v>
+        <v>4967000</v>
       </c>
       <c r="K76" s="3">
         <v>4986000</v>
@@ -3633,25 +3633,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>87000</v>
+        <v>125000</v>
       </c>
       <c r="E81" s="3">
-        <v>87000</v>
+        <v>125000</v>
       </c>
       <c r="F81" s="3">
-        <v>613000</v>
+        <v>654000</v>
       </c>
       <c r="G81" s="3">
-        <v>121000</v>
+        <v>156000</v>
       </c>
       <c r="H81" s="3">
-        <v>30000</v>
+        <v>52000</v>
       </c>
       <c r="I81" s="3">
-        <v>163000</v>
+        <v>192000</v>
       </c>
       <c r="J81" s="3">
-        <v>-11000</v>
+        <v>11000</v>
       </c>
       <c r="K81" s="3">
         <v>276000</v>
@@ -3697,10 +3697,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2739000</v>
+        <v>1969000</v>
       </c>
       <c r="E83" s="3">
-        <v>2158000</v>
+        <v>1597000</v>
       </c>
       <c r="F83" s="3">
         <v>2036000</v>
@@ -3970,7 +3970,7 @@
         <v>4078000</v>
       </c>
       <c r="E89" s="3">
-        <v>3094000</v>
+        <v>3131000</v>
       </c>
       <c r="F89" s="3">
         <v>2772000</v>
@@ -3979,7 +3979,7 @@
         <v>2530000</v>
       </c>
       <c r="H89" s="3">
-        <v>2130000</v>
+        <v>2143000</v>
       </c>
       <c r="I89" s="3">
         <v>1362000</v>
@@ -4230,25 +4230,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1247000</v>
+        <v>701000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1174000</v>
+        <v>660000</v>
       </c>
       <c r="F96" s="3">
-        <v>-1048000</v>
+        <v>608000</v>
       </c>
       <c r="G96" s="3">
-        <v>-949000</v>
+        <v>588000</v>
       </c>
       <c r="H96" s="3">
-        <v>-869000</v>
+        <v>575000</v>
       </c>
       <c r="I96" s="3">
-        <v>-779000</v>
+        <v>520000</v>
       </c>
       <c r="J96" s="3">
-        <v>-680000</v>
+        <v>459000</v>
       </c>
       <c r="K96" s="3">
         <v>-544000</v>
@@ -4503,7 +4503,7 @@
         <v>578000</v>
       </c>
       <c r="E102" s="3">
-        <v>-127000</v>
+        <v>-90000</v>
       </c>
       <c r="F102" s="3">
         <v>539000</v>
@@ -4512,7 +4512,7 @@
         <v>40000</v>
       </c>
       <c r="H102" s="3">
-        <v>287000</v>
+        <v>300000</v>
       </c>
       <c r="I102" s="3">
         <v>166000</v>

--- a/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>BIP</t>
   </si>
@@ -656,210 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21039000</v>
+      </c>
+      <c r="E8" s="3">
         <v>17931000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14427000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11537000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8885000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6597000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4652000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3535000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2115000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1855000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1924000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1826000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1524000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1115000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15676000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13470000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10510000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8247000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6548000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4609000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2208000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1509000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1063000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>798000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>846000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>823000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>766000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>561000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5363000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4461000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3917000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3290000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2337000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1988000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2444000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2026000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1052000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1057000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1078000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1003000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>758000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>554000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -877,8 +889,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -921,9 +934,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,99 +982,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-40000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2100000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-338000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-53000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3644000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2739000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2158000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2036000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1705000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1214000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>801000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>671000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>447000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>375000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>380000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>329000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>230000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>126000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1073,98 +1098,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16081000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13883000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10943000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8653000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6860000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4888000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3232000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2419000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1676000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1307000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1341000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1209000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1091000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>748000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4958000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4048000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3484000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2884000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2025000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1709000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1420000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1116000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>439000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>548000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>583000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>617000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>433000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>367000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1182,233 +1214,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-382000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-480000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-266000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>183000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-349000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-123000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>33000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-59000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>496000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>206000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>95000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>40000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-40000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>51000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8984000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7267000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5908000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4737000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4079000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3046000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2188000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1846000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1382000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1129000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1058000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>986000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>625000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>545000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3387000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2501000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1855000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1468000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1179000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>904000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>555000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>428000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>392000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>367000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>362000</v>
       </c>
       <c r="N22" s="3">
         <v>362000</v>
       </c>
       <c r="O22" s="3">
+        <v>362000</v>
+      </c>
+      <c r="P22" s="3">
         <v>322000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>253000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1953000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2029000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1935000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3333000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1195000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>928000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1170000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>747000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>543000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>387000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>316000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>295000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>71000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>165000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E24" s="3">
         <v>581000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>560000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>614000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>291000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>278000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>364000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>173000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>79000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-30000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1451,99 +1499,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1683000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1448000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1375000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2719000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>904000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>650000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>806000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>574000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>528000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>391000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>237000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>293000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>101000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>151000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>87000</v>
+        <v>57000</v>
       </c>
       <c r="E27" s="3">
         <v>87000</v>
       </c>
       <c r="F27" s="3">
+        <v>87000</v>
+      </c>
+      <c r="G27" s="3">
         <v>613000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>121000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>163000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>276000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>166000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>109000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>165000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-126000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-158000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1586,9 +1643,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1620,20 +1680,23 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-8000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-228000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>190000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>289000</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1676,9 +1739,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1721,99 +1787,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E32" s="3">
         <v>480000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>266000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-183000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>349000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>123000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-33000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>59000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-496000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-206000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-95000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-40000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>40000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-51000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>125000</v>
+        <v>57000</v>
       </c>
       <c r="E33" s="3">
         <v>125000</v>
       </c>
       <c r="F33" s="3">
+        <v>125000</v>
+      </c>
+      <c r="G33" s="3">
         <v>654000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>156000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>52000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>192000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>276000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>166000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>101000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-63000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>64000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>131000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1856,104 +1931,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>125000</v>
+        <v>57000</v>
       </c>
       <c r="E35" s="3">
         <v>125000</v>
       </c>
       <c r="F35" s="3">
+        <v>125000</v>
+      </c>
+      <c r="G35" s="3">
         <v>654000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>156000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>52000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>192000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>276000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>166000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>101000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-63000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>64000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>131000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1971,8 +2055,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1990,413 +2075,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2071000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1857000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1279000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1406000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>867000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>827000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>540000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>374000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>702000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>199000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>189000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>538000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>526000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>306000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>843000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1239000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>614000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>596000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>259000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>240000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>139000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>135000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>432000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>478000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>260000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>23000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>3734000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2342000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1923000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1543000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1802000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1105000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>781000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>468000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>300000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>268000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>313000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>372000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>179000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>512000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>531000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>400000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>221000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>242000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>141000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>108000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>101000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>21000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>108000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>87000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1958000</v>
+      </c>
+      <c r="E45" s="3">
         <v>23000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>980000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>225000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2492000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>123000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>226000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>609000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>604000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>135000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>140000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>72000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4029000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7979000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6686000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4896000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3711000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5841000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2276000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1512000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1632000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1553000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1560000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1268000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>746000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>478000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5927000</v>
+      </c>
+      <c r="E47" s="3">
         <v>5934000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5981000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5174000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5897000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5616000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5297000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5866000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4954000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4234000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2412000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2039000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2179000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1400000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>55910000</v>
+      </c>
+      <c r="E48" s="3">
         <v>48546000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>37291000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38655000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31584000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23013000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12814000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9937000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8810000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7785000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8246000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7927000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19150000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7107000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28622000</v>
+      </c>
+      <c r="E49" s="3">
         <v>30333000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20611000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23193000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18401000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20939000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15494000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11195000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4967000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3375000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3659000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4054000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9630000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3515000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2439,9 +2552,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2484,54 +2600,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>5090000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1259000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1153000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1012000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>702000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>527000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>691000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>912000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>788000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>618000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>394000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1454000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>719000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2574,54 +2696,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>104590000</v>
+      </c>
+      <c r="E54" s="3">
         <v>100784000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>72969000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73961000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>61331000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>56308000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36580000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29477000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21275000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17735000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16495000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15682000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19718000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13269000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2639,8 +2767,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2658,278 +2787,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>2253000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1872000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1877000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1461000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>973000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>463000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>246000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>266000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>196000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>264000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>222000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>842000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>166000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>6571000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3634000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3602000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2007000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1578000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>985000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>463000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>574000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>302000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>41000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>71000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>663000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>145000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1209000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1155000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1476000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2079000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1305000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2235000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>384000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>455000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>675000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>712000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>516000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>305000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>414000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>226000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1209000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11705000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8377000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8661000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5524000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5439000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2417000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1564000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1515000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1210000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>821000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>598000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1291000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>526000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>51094000</v>
+      </c>
+      <c r="E61" s="3">
         <v>43377000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30306000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29752000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25669000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21476000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14241000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9730000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7772000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6950000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6788000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6116000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8115000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4760000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2780000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3285000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2495000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2608000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3071000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2202000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1429000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1460000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2344000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2399000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2564000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2363000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3863000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2328000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2972,9 +3120,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3017,9 +3168,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3062,54 +3216,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>74737000</v>
+      </c>
+      <c r="E66" s="3">
         <v>66768000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47415000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47570000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39658000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34131000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21912000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16003000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16262000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13685000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12938000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11904000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16059000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10196000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3127,8 +3287,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3171,9 +3332,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3216,9 +3380,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3229,41 +3396,44 @@
         <v>918000</v>
       </c>
       <c r="F70" s="3">
+        <v>918000</v>
+      </c>
+      <c r="G70" s="3">
         <v>1138000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1130000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>935000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>936000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>595000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>27000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>23000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>24000</v>
-      </c>
-      <c r="N70" s="3">
-        <v>27000</v>
       </c>
       <c r="O70" s="3">
         <v>27000</v>
       </c>
       <c r="P70" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Q70" s="3">
         <v>26000</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3306,54 +3476,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3246000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2657000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2125000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2285000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1430000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-856000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-953000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-483000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-559000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-400000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-213000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>48000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>189000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3396,9 +3572,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3441,9 +3620,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3486,54 +3668,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4704000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5321000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5372000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5702000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4233000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5048000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4513000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4967000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4986000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4027000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3533000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3751000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3632000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3047000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3576,104 +3764,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>125000</v>
+        <v>57000</v>
       </c>
       <c r="E81" s="3">
         <v>125000</v>
       </c>
       <c r="F81" s="3">
+        <v>125000</v>
+      </c>
+      <c r="G81" s="3">
         <v>654000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>156000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>52000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>192000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>276000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>166000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>101000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-63000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>64000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>131000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3691,53 +3888,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3644000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1969000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1597000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2036000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1705000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1214000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>801000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>671000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>447000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>375000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>380000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>329000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>232000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>127000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3780,9 +3981,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3825,9 +4029,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3870,9 +4077,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3915,9 +4125,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3960,54 +4173,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4653000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4078000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3131000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2772000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2530000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2143000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1362000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1481000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>753000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>632000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>691000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>694000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>635000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>340000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4025,53 +4244,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6812000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2487000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2775000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2067000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1472000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1182000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-839000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-714000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-690000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-520000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-454000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-425000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-654000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-508000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4114,9 +4337,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4159,54 +4385,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6901000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12990000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3365000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1173000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4609000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11372000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5564000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5721000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1058000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2346000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1073000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-162000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1764000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-763000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4224,53 +4456,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>701000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>660000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>608000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>588000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>575000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>520000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>459000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-544000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-480000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-402000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-356000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-288000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-218000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4313,9 +4549,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4358,9 +4597,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4403,142 +4645,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2612000</v>
+      </c>
+      <c r="E100" s="3">
         <v>9419000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-995000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2126000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9542000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4418000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3814000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>899000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1764000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>42000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-232000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1238000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>411000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="E101" s="3">
         <v>71000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>88000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-65000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-13000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-50000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>14000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-32000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-25000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>11000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E102" s="3">
         <v>578000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-90000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>539000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>40000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>166000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-412000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>587000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-349000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>275000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>110000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>BIP</t>
   </si>
@@ -991,8 +991,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-551000</v>
       </c>
       <c r="E14" s="3">
         <v>-2000</v>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-382000</v>
+        <v>169000</v>
       </c>
       <c r="E20" s="3">
         <v>-480000</v>
@@ -1269,7 +1269,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>8984000</v>
+        <v>8433000</v>
       </c>
       <c r="E21" s="3">
         <v>7267000</v>
@@ -1557,7 +1557,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>57000</v>
+        <v>34000</v>
       </c>
       <c r="E27" s="3">
         <v>87000</v>
@@ -1797,7 +1797,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>382000</v>
+        <v>-169000</v>
       </c>
       <c r="E32" s="3">
         <v>480000</v>
@@ -1845,7 +1845,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>57000</v>
+        <v>74000</v>
       </c>
       <c r="E33" s="3">
         <v>125000</v>
@@ -1941,7 +1941,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>57000</v>
+        <v>74000</v>
       </c>
       <c r="E35" s="3">
         <v>125000</v>
@@ -2130,7 +2130,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>530000</v>
       </c>
       <c r="E42" s="3">
         <v>843000</v>
@@ -2177,8 +2177,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3">
+        <v>3873000</v>
       </c>
       <c r="E43" s="3">
         <v>3734000</v>
@@ -2225,8 +2225,8 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>454000</v>
       </c>
       <c r="E44" s="3">
         <v>512000</v>
@@ -2274,7 +2274,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1958000</v>
+        <v>2003000</v>
       </c>
       <c r="E45" s="3">
         <v>23000</v>
@@ -2322,7 +2322,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4029000</v>
+        <v>9607000</v>
       </c>
       <c r="E46" s="3">
         <v>7979000</v>
@@ -2370,7 +2370,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5927000</v>
+        <v>6212000</v>
       </c>
       <c r="E47" s="3">
         <v>5934000</v>
@@ -2418,7 +2418,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>55910000</v>
+        <v>50847000</v>
       </c>
       <c r="E48" s="3">
         <v>48546000</v>
@@ -2609,8 +2609,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>6013000</v>
       </c>
       <c r="E52" s="3">
         <v>5090000</v>
@@ -2793,8 +2793,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>2154000</v>
       </c>
       <c r="E57" s="3">
         <v>2253000</v>
@@ -2842,7 +2842,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4448000</v>
       </c>
       <c r="E58" s="3">
         <v>6571000</v>
@@ -2890,7 +2890,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1209000</v>
+        <v>2493000</v>
       </c>
       <c r="E59" s="3">
         <v>1155000</v>
@@ -2938,7 +2938,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1209000</v>
+        <v>10903000</v>
       </c>
       <c r="E60" s="3">
         <v>11705000</v>
@@ -2986,7 +2986,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>51094000</v>
+        <v>52112000</v>
       </c>
       <c r="E61" s="3">
         <v>43377000</v>
@@ -3034,7 +3034,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2780000</v>
+        <v>3604000</v>
       </c>
       <c r="E62" s="3">
         <v>3285000</v>
@@ -3485,8 +3485,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>-3982000</v>
       </c>
       <c r="E72" s="3">
         <v>-3246000</v>
@@ -3827,7 +3827,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>57000</v>
+        <v>74000</v>
       </c>
       <c r="E81" s="3">
         <v>125000</v>
@@ -3895,13 +3895,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3644000</v>
+        <v>2820000</v>
       </c>
       <c r="E83" s="3">
         <v>1969000</v>
       </c>
       <c r="F83" s="3">
-        <v>1597000</v>
+        <v>2158000</v>
       </c>
       <c r="G83" s="3">
         <v>2036000</v>
@@ -4251,7 +4251,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6812000</v>
+        <v>-4975000</v>
       </c>
       <c r="E91" s="3">
         <v>-2487000</v>
@@ -4463,7 +4463,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>748000</v>
       </c>
       <c r="E96" s="3">
         <v>701000</v>

--- a/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>BIP</t>
   </si>
@@ -656,222 +656,234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23100000</v>
+      </c>
+      <c r="E8" s="3">
         <v>21039000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17931000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14427000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11537000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8885000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6597000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4652000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3535000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2115000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1855000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1924000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1826000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1524000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1115000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16876000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15676000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13470000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10510000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8247000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6548000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4609000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2208000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1509000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1063000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>798000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>846000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>823000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>766000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>561000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6224000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5363000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4461000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3917000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3290000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2337000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1988000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2444000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2026000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1052000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1057000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1078000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1003000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>758000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>554000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -890,8 +902,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -937,9 +950,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,105 +1001,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-278000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-551000</v>
       </c>
-      <c r="E14" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-40000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2100000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>-338000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-53000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4024000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3644000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2739000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2158000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2036000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1705000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1214000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>801000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>671000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>447000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>375000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>380000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>329000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>230000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>126000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1099,104 +1124,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17302000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16081000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13883000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10943000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8653000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6860000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4888000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3232000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2419000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1676000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1307000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1341000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1209000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1091000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>748000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5798000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4958000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4048000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3484000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2884000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2025000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1709000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1420000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1116000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>439000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>548000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>583000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>617000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>433000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>367000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1215,248 +1247,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-913000</v>
+      </c>
+      <c r="E20" s="3">
         <v>169000</v>
       </c>
-      <c r="E20" s="3">
-        <v>-480000</v>
-      </c>
       <c r="F20" s="3">
+        <v>-482000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-266000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>183000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-349000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-123000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>33000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-59000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>496000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>206000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>95000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>40000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-40000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>51000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10735000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8433000</v>
       </c>
-      <c r="E21" s="3">
-        <v>7267000</v>
-      </c>
       <c r="F21" s="3">
+        <v>7269000</v>
+      </c>
+      <c r="G21" s="3">
         <v>5908000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4737000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4079000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3046000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2188000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1846000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1382000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1129000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1058000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>986000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>625000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>545000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3868000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3387000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2501000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1855000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1468000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1179000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>904000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>555000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>428000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>392000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>367000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>362000</v>
       </c>
       <c r="O22" s="3">
         <v>362000</v>
       </c>
       <c r="P22" s="3">
+        <v>362000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>322000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>253000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3121000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1953000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2029000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1935000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3333000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1195000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>928000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1170000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>747000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>543000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>387000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>316000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>295000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>71000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>165000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>589000</v>
+      </c>
+      <c r="E24" s="3">
         <v>270000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>581000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>560000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>614000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>291000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>278000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>364000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>173000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>79000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1502,105 +1550,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2532000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1683000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1448000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1375000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2719000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>904000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>650000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>806000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>574000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>528000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>391000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>237000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>293000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>101000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>151000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>34000</v>
+        <v>415000</v>
       </c>
       <c r="E27" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>64000</v>
+      </c>
+      <c r="G27" s="3">
         <v>87000</v>
       </c>
-      <c r="F27" s="3">
-        <v>87000</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>613000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>121000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>163000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>276000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>166000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>109000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>165000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-126000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-158000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1646,9 +1703,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1683,20 +1743,23 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-8000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-228000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>190000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>289000</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1742,9 +1805,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1790,105 +1856,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>913000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-169000</v>
       </c>
-      <c r="E32" s="3">
-        <v>480000</v>
-      </c>
       <c r="F32" s="3">
+        <v>482000</v>
+      </c>
+      <c r="G32" s="3">
         <v>266000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-183000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>349000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>123000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-33000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>59000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-496000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-206000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-95000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-40000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>40000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-51000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>74000</v>
+        <v>449000</v>
       </c>
       <c r="E33" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>102000</v>
+      </c>
+      <c r="G33" s="3">
         <v>125000</v>
       </c>
-      <c r="F33" s="3">
-        <v>125000</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>654000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>156000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>52000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>192000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>276000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>166000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>101000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-63000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>64000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>131000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1934,110 +2009,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>74000</v>
+        <v>449000</v>
       </c>
       <c r="E35" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>102000</v>
+      </c>
+      <c r="G35" s="3">
         <v>125000</v>
       </c>
-      <c r="F35" s="3">
-        <v>125000</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>654000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>156000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>52000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>192000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>276000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>166000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>101000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-63000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>64000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>131000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2056,8 +2140,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2076,440 +2161,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3201000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2071000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1857000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1279000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1406000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>867000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>827000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>540000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>374000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>702000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>199000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>189000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>538000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>526000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>306000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>381000</v>
+      </c>
+      <c r="E42" s="3">
         <v>530000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>843000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1239000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>614000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>596000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>259000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>240000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>139000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>135000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>432000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>478000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>260000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>23000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4689000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3873000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3734000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2342000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1923000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1543000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1802000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1105000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>781000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>468000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>300000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>268000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>313000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>372000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>179000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>583000</v>
+      </c>
+      <c r="E44" s="3">
         <v>454000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>512000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>531000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>400000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>221000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>242000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>141000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>108000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>101000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>21000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>108000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>87000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2358000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2003000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>980000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>225000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2492000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>123000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>226000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>609000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>604000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>135000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>140000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>72000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11978000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9607000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7979000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6686000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4896000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3711000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5841000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2276000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1512000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1632000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1553000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1560000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1268000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>746000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>478000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6750000</v>
+      </c>
+      <c r="E47" s="3">
         <v>6212000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5934000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5981000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5174000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5897000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5616000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5297000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5866000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4954000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4234000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2412000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2039000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2179000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1400000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>66797000</v>
+      </c>
+      <c r="E48" s="3">
         <v>50847000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>48546000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>37291000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38655000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31584000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23013000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12814000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9937000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8810000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7785000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8246000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7927000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19150000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7107000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34975000</v>
+      </c>
+      <c r="E49" s="3">
         <v>28622000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>30333000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20611000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23193000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18401000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>20939000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15494000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11195000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4967000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3375000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3659000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4054000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9630000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3515000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2555,9 +2668,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2603,57 +2719,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3843000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6013000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5090000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1259000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1153000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1012000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>702000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>527000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>691000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>912000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>788000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>618000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>394000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1454000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>719000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2699,57 +2821,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>128150000</v>
+      </c>
+      <c r="E54" s="3">
         <v>104590000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>100784000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>72969000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73961000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>61331000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>56308000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36580000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29477000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21275000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17735000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16495000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15682000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19718000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13269000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2768,8 +2896,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2788,296 +2917,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2506000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2154000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2253000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1872000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1877000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1461000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>973000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>463000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>246000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>266000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>196000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>264000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>222000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>842000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>166000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7452000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4448000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6571000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3634000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3602000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2007000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1578000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>985000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>463000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>574000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>302000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>41000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>71000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>663000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>145000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3074000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2493000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1155000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1476000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2079000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1305000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2235000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>384000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>455000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>675000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>712000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>516000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>305000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>414000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>226000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15260000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10903000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11705000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8377000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8661000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5524000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5439000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2417000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1564000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1515000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1210000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>821000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>598000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1291000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>526000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>62064000</v>
+      </c>
+      <c r="E61" s="3">
         <v>52112000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>43377000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>30306000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>29752000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25669000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21476000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14241000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9730000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7772000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6950000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6788000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6116000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8115000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4760000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4998000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3604000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3285000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2495000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2608000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3071000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2202000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1429000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1460000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2344000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2399000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2564000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2363000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3863000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2328000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3123,9 +3271,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3171,9 +3322,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3219,57 +3373,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92610000</v>
+      </c>
+      <c r="E66" s="3">
         <v>74737000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>66768000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47415000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47570000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39658000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34131000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21912000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16003000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16262000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13685000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12938000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11904000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16059000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10196000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3288,8 +3448,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3335,9 +3496,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3383,14 +3547,17 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>918000</v>
+        <v>729000</v>
       </c>
       <c r="E70" s="3">
         <v>918000</v>
@@ -3399,41 +3566,44 @@
         <v>918000</v>
       </c>
       <c r="G70" s="3">
+        <v>918000</v>
+      </c>
+      <c r="H70" s="3">
         <v>1138000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1130000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>935000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>936000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>595000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>27000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>23000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>24000</v>
-      </c>
-      <c r="O70" s="3">
-        <v>27000</v>
       </c>
       <c r="P70" s="3">
         <v>27000</v>
       </c>
       <c r="Q70" s="3">
+        <v>27000</v>
+      </c>
+      <c r="R70" s="3">
         <v>26000</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3479,57 +3649,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4233000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3982000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3246000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2657000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2125000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2285000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1430000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-856000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-953000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-483000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-559000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-400000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-213000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>48000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>189000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3575,9 +3751,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3623,9 +3802,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3671,57 +3853,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4889000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4704000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5321000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5372000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5702000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4233000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5048000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4513000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4967000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4986000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4027000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3533000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3751000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3632000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3047000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3767,110 +3955,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>74000</v>
+        <v>449000</v>
       </c>
       <c r="E81" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>102000</v>
+      </c>
+      <c r="G81" s="3">
         <v>125000</v>
       </c>
-      <c r="F81" s="3">
-        <v>125000</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>654000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>156000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>52000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>192000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>276000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>166000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>101000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-63000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>64000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>131000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3889,56 +4086,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3114000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2820000</v>
       </c>
-      <c r="E83" s="3">
-        <v>1969000</v>
-      </c>
       <c r="F83" s="3">
+        <v>2739000</v>
+      </c>
+      <c r="G83" s="3">
         <v>2158000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2036000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1705000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1214000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>801000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>671000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>447000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>375000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>380000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>329000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>232000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>127000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3984,9 +4185,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4032,9 +4236,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4080,9 +4287,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4128,9 +4338,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4176,57 +4389,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5971000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4653000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4078000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3131000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2772000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2530000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2143000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1362000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1481000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>753000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>632000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>691000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>694000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>635000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>340000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4245,56 +4464,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6024000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4975000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2487000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2775000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2067000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1472000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1182000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-839000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-714000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-690000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-520000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-454000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-425000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-654000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-508000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4340,9 +4563,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4388,57 +4614,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12661000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6901000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12990000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3365000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1173000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4609000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11372000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5564000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5721000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1058000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2346000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1073000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-162000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1764000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-763000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4457,56 +4689,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>793000</v>
+      </c>
+      <c r="E96" s="3">
         <v>748000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>701000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>660000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>608000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>588000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>575000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>520000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>459000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-544000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-480000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-402000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-356000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-288000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-218000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4552,9 +4788,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4600,9 +4839,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4648,151 +4890,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7818000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2612000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9419000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>56000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-995000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2126000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9542000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4418000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3814000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>899000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1764000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>42000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-232000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1238000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>411000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-150000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>71000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>88000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-65000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-13000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-50000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-32000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-25000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>11000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1175000</v>
+      </c>
+      <c r="E102" s="3">
         <v>214000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>578000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-90000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>539000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>166000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-412000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>587000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-349000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>275000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>110000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BIP_YR_FIN.xlsx
@@ -1620,10 +1620,10 @@
         <v>64000</v>
       </c>
       <c r="G27" s="3">
-        <v>87000</v>
+        <v>63000</v>
       </c>
       <c r="H27" s="3">
-        <v>613000</v>
+        <v>515000</v>
       </c>
       <c r="I27" s="3">
         <v>121000</v>
@@ -1926,10 +1926,10 @@
         <v>102000</v>
       </c>
       <c r="G33" s="3">
-        <v>125000</v>
+        <v>101000</v>
       </c>
       <c r="H33" s="3">
-        <v>654000</v>
+        <v>556000</v>
       </c>
       <c r="I33" s="3">
         <v>156000</v>
@@ -2028,10 +2028,10 @@
         <v>102000</v>
       </c>
       <c r="G35" s="3">
-        <v>125000</v>
+        <v>101000</v>
       </c>
       <c r="H35" s="3">
-        <v>654000</v>
+        <v>556000</v>
       </c>
       <c r="I35" s="3">
         <v>156000</v>
@@ -4030,10 +4030,10 @@
         <v>102000</v>
       </c>
       <c r="G81" s="3">
-        <v>125000</v>
+        <v>101000</v>
       </c>
       <c r="H81" s="3">
-        <v>654000</v>
+        <v>556000</v>
       </c>
       <c r="I81" s="3">
         <v>156000</v>
